--- a/Dokumentation/Mappe1.xlsx
+++ b/Dokumentation/Mappe1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Michael Watzek\Documents\Diplom_Arbeit\Dokumentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micha\Documents\Messung_von_Quanteneffecten_in_MOSFETs\Diplom_Arbeit\Dokumentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{01198566-B4DC-4946-BCE3-1D3F84FB7267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7AF9E5E7-61EE-4B50-9126-C0CB14A5359B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{7AF9E5E7-61EE-4B50-9126-C0CB14A5359B}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -161,10 +161,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -4020,15 +4019,15 @@
         <v>17.989999999999998</v>
       </c>
       <c r="F72">
-        <f t="shared" ref="F72:F88" si="6">D72*E72</f>
+        <f t="shared" ref="F72:F83" si="6">D72*E72</f>
         <v>3.4540799999999998</v>
       </c>
       <c r="G72">
-        <f t="shared" ref="G72:G88" si="7">B72*C72</f>
+        <f t="shared" ref="G72:G83" si="7">B72*C72</f>
         <v>2.39994</v>
       </c>
       <c r="H72">
-        <f t="shared" ref="H72:H88" si="8">G72/F72*100</f>
+        <f t="shared" ref="H72:H83" si="8">G72/F72*100</f>
         <v>69.481309060589211</v>
       </c>
     </row>
@@ -4137,213 +4136,186 @@
       </c>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B77" s="2">
+      <c r="B77">
         <v>0.70099999999999996</v>
       </c>
-      <c r="C77" s="2">
+      <c r="C77">
         <v>11.88</v>
       </c>
-      <c r="D77" s="2">
+      <c r="D77">
         <v>0.55800000000000005</v>
       </c>
-      <c r="E77" s="2">
+      <c r="E77">
         <v>17.91</v>
       </c>
-      <c r="F77" s="2">
+      <c r="F77">
         <f t="shared" si="6"/>
         <v>9.993780000000001</v>
       </c>
-      <c r="G77" s="2">
+      <c r="G77">
         <f t="shared" si="7"/>
         <v>8.3278800000000004</v>
       </c>
-      <c r="H77" s="2">
+      <c r="H77">
         <f t="shared" si="8"/>
         <v>83.330631652888087</v>
       </c>
     </row>
     <row r="78" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B78" s="2">
+      <c r="B78">
         <v>0.80900000000000005</v>
       </c>
-      <c r="C78" s="2">
+      <c r="C78">
         <v>11.86</v>
       </c>
-      <c r="D78" s="2">
+      <c r="D78">
         <v>0.64100000000000001</v>
       </c>
-      <c r="E78" s="2">
+      <c r="E78">
         <v>17.87</v>
       </c>
-      <c r="F78" s="2">
+      <c r="F78">
         <f t="shared" si="6"/>
         <v>11.45467</v>
       </c>
-      <c r="G78" s="2">
+      <c r="G78">
         <f t="shared" si="7"/>
         <v>9.5947399999999998</v>
       </c>
-      <c r="H78" s="2">
+      <c r="H78">
         <f t="shared" si="8"/>
         <v>83.762692421518906</v>
       </c>
     </row>
     <row r="79" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B79" s="2">
+      <c r="B79">
         <v>0.90700000000000003</v>
       </c>
-      <c r="C79" s="2">
+      <c r="C79">
         <v>11.84</v>
       </c>
-      <c r="D79" s="2">
+      <c r="D79">
         <v>0.71699999999999997</v>
       </c>
-      <c r="E79" s="2">
+      <c r="E79">
         <v>17.84</v>
       </c>
-      <c r="F79" s="2">
+      <c r="F79">
         <f t="shared" si="6"/>
         <v>12.791279999999999</v>
       </c>
-      <c r="G79" s="2">
+      <c r="G79">
         <f t="shared" si="7"/>
         <v>10.73888</v>
       </c>
-      <c r="H79" s="2">
+      <c r="H79">
         <f t="shared" si="8"/>
         <v>83.954694135379739</v>
       </c>
     </row>
     <row r="80" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B80" s="2">
+      <c r="B80">
         <v>1.022</v>
       </c>
-      <c r="C80" s="2">
+      <c r="C80">
         <v>11.81</v>
       </c>
-      <c r="D80" s="2">
+      <c r="D80">
         <v>0.81200000000000006</v>
       </c>
-      <c r="E80" s="2">
+      <c r="E80">
         <v>17.72</v>
       </c>
-      <c r="F80" s="2">
+      <c r="F80">
         <f t="shared" si="6"/>
         <v>14.388640000000001</v>
       </c>
-      <c r="G80" s="2">
+      <c r="G80">
         <f t="shared" si="7"/>
         <v>12.06982</v>
       </c>
-      <c r="H80" s="2">
+      <c r="H80">
         <f t="shared" si="8"/>
         <v>83.88436989180353</v>
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B81" s="2">
+      <c r="B81">
         <v>1.1259999999999999</v>
       </c>
-      <c r="C81" s="2">
+      <c r="C81">
         <v>11.78</v>
       </c>
-      <c r="D81" s="2">
+      <c r="D81">
         <v>0.89500000000000002</v>
       </c>
-      <c r="E81" s="2">
+      <c r="E81">
         <v>17.739999999999998</v>
       </c>
-      <c r="F81" s="2">
+      <c r="F81">
         <f t="shared" si="6"/>
         <v>15.877299999999998</v>
       </c>
-      <c r="G81" s="2">
+      <c r="G81">
         <f t="shared" si="7"/>
         <v>13.264279999999998</v>
       </c>
-      <c r="H81" s="2">
+      <c r="H81">
         <f t="shared" si="8"/>
         <v>83.542415901948061</v>
       </c>
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B82" s="2">
+      <c r="B82">
         <v>1.2030000000000001</v>
       </c>
-      <c r="C82" s="2">
+      <c r="C82">
         <v>11.78</v>
       </c>
-      <c r="D82" s="2">
+      <c r="D82">
         <v>0.95699999999999996</v>
       </c>
-      <c r="E82" s="2">
+      <c r="E82">
         <v>17.739999999999998</v>
       </c>
-      <c r="F82" s="2">
+      <c r="F82">
         <f t="shared" si="6"/>
         <v>16.977179999999997</v>
       </c>
-      <c r="G82" s="2">
+      <c r="G82">
         <f t="shared" si="7"/>
         <v>14.171340000000001</v>
       </c>
-      <c r="H82" s="2">
+      <c r="H82">
         <f t="shared" si="8"/>
         <v>83.472873586779457</v>
       </c>
     </row>
     <row r="83" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B83" s="2">
+      <c r="B83">
         <v>1.3340000000000001</v>
       </c>
-      <c r="C83" s="2">
+      <c r="C83">
         <v>11.76</v>
       </c>
-      <c r="D83" s="2">
+      <c r="D83">
         <v>1.0620000000000001</v>
       </c>
-      <c r="E83" s="2">
+      <c r="E83">
         <v>17.739999999999998</v>
       </c>
-      <c r="F83" s="2">
+      <c r="F83">
         <f t="shared" si="6"/>
         <v>18.839880000000001</v>
       </c>
-      <c r="G83" s="2">
+      <c r="G83">
         <f t="shared" si="7"/>
         <v>15.687840000000001</v>
       </c>
-      <c r="H83" s="2">
+      <c r="H83">
         <f t="shared" si="8"/>
         <v>83.269320186752779</v>
       </c>
-    </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B84" s="2"/>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-      <c r="H84" s="2"/>
-    </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B85" s="2"/>
-      <c r="C85" s="2"/>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-      <c r="F85" s="2"/>
-      <c r="G85" s="2"/>
-      <c r="H85" s="2"/>
-    </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B86" s="2"/>
-      <c r="C86" s="2"/>
-      <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
-      <c r="F86" s="2"/>
-      <c r="G86" s="2"/>
-      <c r="H86" s="2"/>
     </row>
     <row r="89" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B89" t="s">
